--- a/Data/eMobility/Expenses/vehicleRepairs.xlsx
+++ b/Data/eMobility/Expenses/vehicleRepairs.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\OneDrive\Operational Intelligence Hub\Data\Emobility-Expenses-Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\OneDrive\Operational Intelligence Hub\Data\eMobility\Expenses\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7A318AA4-B226-4688-8405-4F67D031F3F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1804D364-560A-48CD-BAF6-0F19F7004E92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{16518C60-F727-4582-935E-480798FDC36D}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$189</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$188</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -652,14 +652,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9989A3D-C7FA-4F6D-B5AD-BE193FDFB91C}">
-  <dimension ref="A1:K189"/>
+  <dimension ref="A1:K188"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.81640625" customWidth="1"/>
     <col min="2" max="2" width="12.54296875" customWidth="1"/>
-    <col min="3" max="3" width="15.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="37.54296875" customWidth="1"/>
-    <col min="5" max="9" width="12.54296875" customWidth="1"/>
+    <col min="3" max="3" width="19.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.54296875" customWidth="1"/>
+    <col min="9" max="9" width="12.26953125" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="12.54296875" style="10" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3544,7 +3548,7 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A81" s="3">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
@@ -3559,7 +3563,7 @@
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A82" s="3">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
@@ -3574,7 +3578,7 @@
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A83" s="3">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
@@ -3589,7 +3593,7 @@
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A84" s="3">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
@@ -3604,7 +3608,7 @@
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A85" s="3">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
@@ -3619,7 +3623,7 @@
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A86" s="3">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
@@ -3634,7 +3638,7 @@
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A87" s="3">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
@@ -3649,7 +3653,7 @@
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A88" s="3">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
@@ -3664,7 +3668,7 @@
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A89" s="3">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
@@ -3679,7 +3683,7 @@
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A90" s="3">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
@@ -3694,7 +3698,7 @@
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A91" s="3">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
@@ -3709,7 +3713,7 @@
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A92" s="3">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
@@ -3724,7 +3728,7 @@
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A93" s="3">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
@@ -3739,7 +3743,7 @@
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A94" s="3">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
@@ -3754,7 +3758,7 @@
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A95" s="3">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
@@ -3769,7 +3773,7 @@
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A96" s="3">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
@@ -3784,7 +3788,7 @@
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A97" s="3">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
@@ -3799,7 +3803,7 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A98" s="3">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
@@ -3814,7 +3818,7 @@
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A99" s="3">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
@@ -3829,7 +3833,7 @@
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A100" s="3">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
@@ -3844,7 +3848,7 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A101" s="3">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
@@ -3859,7 +3863,7 @@
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A102" s="3">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
@@ -3874,7 +3878,7 @@
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A103" s="3">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
@@ -3889,7 +3893,7 @@
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A104" s="3">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
@@ -3904,7 +3908,7 @@
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A105" s="3">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
@@ -3919,7 +3923,7 @@
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A106" s="3">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
@@ -3934,7 +3938,7 @@
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A107" s="3">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
@@ -3949,7 +3953,7 @@
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A108" s="3">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
@@ -3964,7 +3968,7 @@
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A109" s="3">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
@@ -3979,7 +3983,7 @@
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A110" s="3">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
@@ -3994,7 +3998,7 @@
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A111" s="3">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
@@ -4009,7 +4013,7 @@
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A112" s="3">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
@@ -4024,7 +4028,7 @@
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A113" s="3">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
@@ -4039,7 +4043,7 @@
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A114" s="3">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
@@ -4054,7 +4058,7 @@
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A115" s="3">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
@@ -4069,7 +4073,7 @@
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A116" s="3">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
@@ -4084,7 +4088,7 @@
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A117" s="3">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
@@ -4099,7 +4103,7 @@
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A118" s="3">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
@@ -4114,7 +4118,7 @@
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A119" s="3">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
@@ -4129,7 +4133,7 @@
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A120" s="3">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
@@ -4144,7 +4148,7 @@
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A121" s="3">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
@@ -4159,7 +4163,7 @@
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A122" s="3">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
@@ -4174,7 +4178,7 @@
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A123" s="3">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
@@ -4189,7 +4193,7 @@
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A124" s="3">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
@@ -4204,7 +4208,7 @@
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A125" s="3">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
@@ -4219,7 +4223,7 @@
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A126" s="3">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
@@ -4234,7 +4238,7 @@
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A127" s="3">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
@@ -4249,7 +4253,7 @@
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A128" s="3">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
@@ -4264,7 +4268,7 @@
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A129" s="3">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
@@ -4279,7 +4283,7 @@
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A130" s="3">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
@@ -4294,7 +4298,7 @@
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A131" s="3">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
@@ -4309,7 +4313,7 @@
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A132" s="3">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
@@ -4324,7 +4328,7 @@
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A133" s="3">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
@@ -4339,7 +4343,7 @@
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A134" s="3">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
@@ -4354,7 +4358,7 @@
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A135" s="3">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
@@ -4369,7 +4373,7 @@
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A136" s="3">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
@@ -4384,7 +4388,7 @@
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A137" s="3">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
@@ -4399,7 +4403,7 @@
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A138" s="3">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
@@ -4414,7 +4418,7 @@
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A139" s="3">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
@@ -4429,7 +4433,7 @@
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A140" s="3">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
@@ -4444,7 +4448,7 @@
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A141" s="3">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
@@ -4459,7 +4463,7 @@
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A142" s="3">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
@@ -4474,7 +4478,7 @@
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A143" s="3">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
@@ -4489,7 +4493,7 @@
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A144" s="3">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
@@ -4504,7 +4508,7 @@
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A145" s="3">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
@@ -4519,7 +4523,7 @@
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A146" s="3">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
@@ -4534,7 +4538,7 @@
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A147" s="3">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
@@ -4549,7 +4553,7 @@
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A148" s="3">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
@@ -4564,7 +4568,7 @@
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A149" s="3">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
@@ -4579,7 +4583,7 @@
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A150" s="3">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
@@ -4594,7 +4598,7 @@
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A151" s="3">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
@@ -4609,7 +4613,7 @@
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A152" s="3">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
@@ -4624,7 +4628,7 @@
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A153" s="3">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
@@ -4639,7 +4643,7 @@
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A154" s="3">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
@@ -4654,7 +4658,7 @@
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A155" s="3">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
@@ -4669,7 +4673,7 @@
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A156" s="3">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
@@ -4684,7 +4688,7 @@
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A157" s="3">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
@@ -4699,7 +4703,7 @@
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A158" s="3">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
@@ -4714,7 +4718,7 @@
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A159" s="3">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
@@ -4729,7 +4733,7 @@
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A160" s="3">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
@@ -4744,7 +4748,7 @@
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A161" s="3">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
@@ -4759,7 +4763,7 @@
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A162" s="3">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
@@ -4774,7 +4778,7 @@
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A163" s="3">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B163" s="3"/>
       <c r="C163" s="3"/>
@@ -4789,7 +4793,7 @@
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A164" s="3">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
@@ -4804,7 +4808,7 @@
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A165" s="3">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
@@ -4819,7 +4823,7 @@
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A166" s="3">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B166" s="3"/>
       <c r="C166" s="3"/>
@@ -4834,7 +4838,7 @@
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A167" s="3">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
@@ -4849,7 +4853,7 @@
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A168" s="3">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B168" s="3"/>
       <c r="C168" s="3"/>
@@ -4864,7 +4868,7 @@
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A169" s="3">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B169" s="3"/>
       <c r="C169" s="3"/>
@@ -4879,7 +4883,7 @@
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A170" s="3">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
@@ -4894,7 +4898,7 @@
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A171" s="3">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
@@ -4909,7 +4913,7 @@
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A172" s="3">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
@@ -4924,7 +4928,7 @@
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A173" s="3">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
@@ -4939,7 +4943,7 @@
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A174" s="3">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
@@ -4954,7 +4958,7 @@
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A175" s="3">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
@@ -4969,7 +4973,7 @@
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A176" s="3">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
@@ -4984,7 +4988,7 @@
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A177" s="3">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
@@ -4999,7 +5003,7 @@
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A178" s="3">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B178" s="3"/>
       <c r="C178" s="3"/>
@@ -5014,7 +5018,7 @@
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A179" s="3">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
@@ -5029,7 +5033,7 @@
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A180" s="3">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
@@ -5044,7 +5048,7 @@
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A181" s="3">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
@@ -5059,7 +5063,7 @@
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A182" s="3">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B182" s="3"/>
       <c r="C182" s="3"/>
@@ -5074,7 +5078,7 @@
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A183" s="3">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B183" s="3"/>
       <c r="C183" s="3"/>
@@ -5089,7 +5093,7 @@
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A184" s="3">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B184" s="3"/>
       <c r="C184" s="3"/>
@@ -5104,7 +5108,7 @@
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A185" s="3">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
@@ -5119,7 +5123,7 @@
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A186" s="3">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
@@ -5134,7 +5138,7 @@
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A187" s="3">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
@@ -5149,7 +5153,7 @@
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A188" s="3">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
@@ -5162,23 +5166,8 @@
       <c r="J188" s="6"/>
       <c r="K188" s="6"/>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A189" s="3">
-        <v>188</v>
-      </c>
-      <c r="B189" s="3"/>
-      <c r="C189" s="3"/>
-      <c r="D189" s="3"/>
-      <c r="E189" s="3"/>
-      <c r="F189" s="3"/>
-      <c r="G189" s="3"/>
-      <c r="H189" s="3"/>
-      <c r="I189" s="3"/>
-      <c r="J189" s="6"/>
-      <c r="K189" s="6"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K189" xr:uid="{C9989A3D-C7FA-4F6D-B5AD-BE193FDFB91C}"/>
+  <autoFilter ref="A1:K188" xr:uid="{C9989A3D-C7FA-4F6D-B5AD-BE193FDFB91C}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Data/eMobility/Expenses/vehicleRepairs.xlsx
+++ b/Data/eMobility/Expenses/vehicleRepairs.xlsx
@@ -1,20 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="7"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\OneDrive\Operational Intelligence Hub\Data\eMobility\Expenses\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C57C305A-6A4C-4EBA-B955-4FF205B0C0DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Sheet1!$A$1:$K$188</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$188</definedName>
   </definedNames>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -25,211 +39,210 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="65">
   <si>
-    <t xml:space="preserve">No</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product Category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Product Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Supplier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vehicle Reg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Units</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">@</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mechanical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ball joint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spares</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Triple three</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KDC 978N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SET</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tie rod</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stabilizer link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rack end</t>
-  </si>
-  <si>
-    <t xml:space="preserve">shock mounting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bushes big and small</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rear bushes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KCY 480D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Headlight</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KDT 082R</t>
-  </si>
-  <si>
-    <t xml:space="preserve">spares</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KCY 492D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chloride battery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KCM 531J</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Front shock</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KDC 527M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Front brake pads</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rear brake pads</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Battary 12V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WHEEL BALANCING - PASSENGER - 16"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AUTOXPRESS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WHEEL ALIGNMENT - TOE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TYRE ROADWING 205/55R16 RW-581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUBELESS VALVE - TR 413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodyworks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Body filler 1 Gallon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sand papers -P-40 6pcs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-60 3pcs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-240 2pcs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-360 3pcs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-400 2pcs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-600 3pcs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-1200 3pcs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primer 1 ltrs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Spot putty 0.5kg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magazine 3kgs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Masking tape 4pcs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Under coat 1ltr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zirelick paint 1 1/2ltrs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clear  1/2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hardener 1/2ltr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slow Thinner 1ltr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Standard thinner 3ltrs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KDC 112W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-240 3pcs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-400 3pcs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Primer 1/2ltrs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clear 1 1/2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Slow Thinner 1/2ltr</t>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Product Category</t>
+  </si>
+  <si>
+    <t>Product Name</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Supplier</t>
+  </si>
+  <si>
+    <t>Vehicle Reg</t>
+  </si>
+  <si>
+    <t>Units</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>@</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>mechanical</t>
+  </si>
+  <si>
+    <t>Ball joint</t>
+  </si>
+  <si>
+    <t>Spares</t>
+  </si>
+  <si>
+    <t>Triple three</t>
+  </si>
+  <si>
+    <t>KDC 978N</t>
+  </si>
+  <si>
+    <t>SET</t>
+  </si>
+  <si>
+    <t>Tie rod</t>
+  </si>
+  <si>
+    <t>stabilizer link</t>
+  </si>
+  <si>
+    <t>rack end</t>
+  </si>
+  <si>
+    <t>shock mounting</t>
+  </si>
+  <si>
+    <t>bushes big and small</t>
+  </si>
+  <si>
+    <t>Rear bushes</t>
+  </si>
+  <si>
+    <t>KCY 480D</t>
+  </si>
+  <si>
+    <t>Headlight</t>
+  </si>
+  <si>
+    <t>KDT 082R</t>
+  </si>
+  <si>
+    <t>spares</t>
+  </si>
+  <si>
+    <t>KCY 492D</t>
+  </si>
+  <si>
+    <t>Chloride battery</t>
+  </si>
+  <si>
+    <t>KCM 531J</t>
+  </si>
+  <si>
+    <t>Front shock</t>
+  </si>
+  <si>
+    <t>KDC 527M</t>
+  </si>
+  <si>
+    <t>Front brake pads</t>
+  </si>
+  <si>
+    <t>rear brake pads</t>
+  </si>
+  <si>
+    <t>Battary 12V</t>
+  </si>
+  <si>
+    <t>WHEEL BALANCING - PASSENGER - 16"</t>
+  </si>
+  <si>
+    <t>AUTOXPRESS</t>
+  </si>
+  <si>
+    <t>WHEEL ALIGNMENT - TOE</t>
+  </si>
+  <si>
+    <t>TYRE ROADWING 205/55R16 RW-581</t>
+  </si>
+  <si>
+    <t>TUBELESS VALVE - TR 413</t>
+  </si>
+  <si>
+    <t>Bodyworks</t>
+  </si>
+  <si>
+    <t>Body filler 1 Gallon</t>
+  </si>
+  <si>
+    <t>Sand papers -P-40 6pcs</t>
+  </si>
+  <si>
+    <t>P-60 3pcs</t>
+  </si>
+  <si>
+    <t>P-240 2pcs</t>
+  </si>
+  <si>
+    <t>P-360 3pcs</t>
+  </si>
+  <si>
+    <t>P-400 2pcs</t>
+  </si>
+  <si>
+    <t>P-600 3pcs</t>
+  </si>
+  <si>
+    <t>P-1200 3pcs</t>
+  </si>
+  <si>
+    <t>Primer 1 ltrs</t>
+  </si>
+  <si>
+    <t>Spot putty 0.5kg</t>
+  </si>
+  <si>
+    <t>Magazine 3kgs</t>
+  </si>
+  <si>
+    <t>Masking tape 4pcs</t>
+  </si>
+  <si>
+    <t>Under coat 1ltr</t>
+  </si>
+  <si>
+    <t>Zirelick paint 1 1/2ltrs</t>
+  </si>
+  <si>
+    <t>Clear  1/2</t>
+  </si>
+  <si>
+    <t>Hardener 1/2ltr</t>
+  </si>
+  <si>
+    <t>Slow Thinner 1ltr</t>
+  </si>
+  <si>
+    <t>Standard thinner 3ltrs</t>
+  </si>
+  <si>
+    <t>KDC 112W</t>
+  </si>
+  <si>
+    <t>P-240 3pcs</t>
+  </si>
+  <si>
+    <t>P-400 3pcs</t>
+  </si>
+  <si>
+    <t>Primer 1/2ltrs</t>
+  </si>
+  <si>
+    <t>Clear 1 1/2</t>
+  </si>
+  <si>
+    <t>Slow Thinner 1/2ltr</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* \-??_-;_-@_-"/>
-    <numFmt numFmtId="166" formatCode="mm/dd/yyyy"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* \-??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -238,22 +251,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -281,6 +279,13 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -291,135 +296,52 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="15" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF181717"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF231F20"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -478,17 +400,29 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF231F20"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -530,12 +464,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -567,7 +501,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -591,7 +525,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -651,35 +585,35 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K188"/>
-  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="32.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="1" width="12.54"/>
+    <col min="1" max="1" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.6328125" customWidth="1"/>
+    <col min="4" max="4" width="32.90625" customWidth="1"/>
+    <col min="5" max="5" width="14.453125" customWidth="1"/>
+    <col min="6" max="6" width="11.81640625" customWidth="1"/>
+    <col min="7" max="7" width="14.54296875" customWidth="1"/>
+    <col min="8" max="8" width="9.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.26953125" customWidth="1"/>
+    <col min="10" max="10" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="4" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:11" s="4" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -714,11 +648,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="6" t="n">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A2" s="5">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6">
         <v>46047</v>
       </c>
       <c r="C2" s="5" t="s">
@@ -739,22 +673,22 @@
       <c r="H2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" s="7" t="n">
+      <c r="I2" s="5">
+        <v>1</v>
+      </c>
+      <c r="J2" s="7">
         <v>3000</v>
       </c>
-      <c r="K2" s="8" t="n">
-        <f aca="false">I2*J2</f>
+      <c r="K2" s="8">
+        <f t="shared" ref="K2:K33" si="0">I2*J2</f>
         <v>3000</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="n">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="6">
         <v>46047</v>
       </c>
       <c r="C3" s="5" t="s">
@@ -775,22 +709,22 @@
       <c r="H3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" s="7" t="n">
+      <c r="I3" s="5">
+        <v>1</v>
+      </c>
+      <c r="J3" s="7">
         <v>3500</v>
       </c>
-      <c r="K3" s="8" t="n">
-        <f aca="false">I3*J3</f>
+      <c r="K3" s="8">
+        <f t="shared" si="0"/>
         <v>3500</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="n">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="6">
         <v>46047</v>
       </c>
       <c r="C4" s="5" t="s">
@@ -811,22 +745,22 @@
       <c r="H4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="9" t="n">
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="9">
         <v>3500</v>
       </c>
-      <c r="K4" s="8" t="n">
-        <f aca="false">I4*J4</f>
+      <c r="K4" s="8">
+        <f t="shared" si="0"/>
         <v>3500</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="n">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="6">
         <v>46047</v>
       </c>
       <c r="C5" s="5" t="s">
@@ -847,22 +781,22 @@
       <c r="H5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="9" t="n">
+      <c r="I5" s="5">
+        <v>1</v>
+      </c>
+      <c r="J5" s="9">
         <v>3700</v>
       </c>
-      <c r="K5" s="8" t="n">
-        <f aca="false">I5*J5</f>
+      <c r="K5" s="8">
+        <f t="shared" si="0"/>
         <v>3700</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="n">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="6">
         <v>46047</v>
       </c>
       <c r="C6" s="5" t="s">
@@ -883,22 +817,22 @@
       <c r="H6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="10" t="n">
+      <c r="I6" s="5">
+        <v>1</v>
+      </c>
+      <c r="J6" s="10">
         <v>3700</v>
       </c>
-      <c r="K6" s="8" t="n">
-        <f aca="false">I6*J6</f>
+      <c r="K6" s="8">
+        <f t="shared" si="0"/>
         <v>3700</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="n">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="6">
         <v>46047</v>
       </c>
       <c r="C7" s="5" t="s">
@@ -919,22 +853,22 @@
       <c r="H7" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I7" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" s="9" t="n">
+      <c r="I7" s="5">
+        <v>1</v>
+      </c>
+      <c r="J7" s="9">
         <v>4500</v>
       </c>
-      <c r="K7" s="8" t="n">
-        <f aca="false">I7*J7</f>
+      <c r="K7" s="8">
+        <f t="shared" si="0"/>
         <v>4500</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="n">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A8" s="5">
         <v>7</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="6">
         <v>46047</v>
       </c>
       <c r="C8" s="5" t="s">
@@ -955,22 +889,22 @@
       <c r="H8" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I8" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="9" t="n">
+      <c r="I8" s="5">
+        <v>1</v>
+      </c>
+      <c r="J8" s="9">
         <v>2500</v>
       </c>
-      <c r="K8" s="8" t="n">
-        <f aca="false">I8*J8</f>
+      <c r="K8" s="8">
+        <f t="shared" si="0"/>
         <v>2500</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="n">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A9" s="5">
         <v>8</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="6">
         <v>46039</v>
       </c>
       <c r="C9" s="5" t="s">
@@ -991,22 +925,22 @@
       <c r="H9" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I9" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" s="7" t="n">
+      <c r="I9" s="5">
+        <v>1</v>
+      </c>
+      <c r="J9" s="7">
         <v>3000</v>
       </c>
-      <c r="K9" s="8" t="n">
-        <f aca="false">I9*J9</f>
+      <c r="K9" s="8">
+        <f t="shared" si="0"/>
         <v>3000</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="n">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A10" s="5">
         <v>9</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="6">
         <v>46040</v>
       </c>
       <c r="C10" s="5" t="s">
@@ -1027,22 +961,22 @@
       <c r="H10" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="7" t="n">
+      <c r="I10" s="5">
+        <v>1</v>
+      </c>
+      <c r="J10" s="7">
         <v>3500</v>
       </c>
-      <c r="K10" s="8" t="n">
-        <f aca="false">I10*J10</f>
+      <c r="K10" s="8">
+        <f t="shared" si="0"/>
         <v>3500</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="n">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A11" s="5">
         <v>10</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="6">
         <v>46039</v>
       </c>
       <c r="C11" s="5" t="s">
@@ -1063,22 +997,22 @@
       <c r="H11" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="7" t="n">
+      <c r="I11" s="5">
+        <v>1</v>
+      </c>
+      <c r="J11" s="7">
         <v>26000</v>
       </c>
-      <c r="K11" s="8" t="n">
-        <f aca="false">I11*J11</f>
+      <c r="K11" s="8">
+        <f t="shared" si="0"/>
         <v>26000</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="n">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A12" s="5">
         <v>11</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="6">
         <v>46060</v>
       </c>
       <c r="C12" s="5" t="s">
@@ -1099,22 +1033,22 @@
       <c r="H12" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="9" t="n">
+      <c r="I12" s="5">
+        <v>1</v>
+      </c>
+      <c r="J12" s="9">
         <v>4500</v>
       </c>
-      <c r="K12" s="8" t="n">
-        <f aca="false">I12*J12</f>
+      <c r="K12" s="8">
+        <f t="shared" si="0"/>
         <v>4500</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="n">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A13" s="5">
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="6">
         <v>46060</v>
       </c>
       <c r="C13" s="5" t="s">
@@ -1135,22 +1069,22 @@
       <c r="H13" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I13" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" s="9" t="n">
+      <c r="I13" s="5">
+        <v>1</v>
+      </c>
+      <c r="J13" s="9">
         <v>2500</v>
       </c>
-      <c r="K13" s="8" t="n">
-        <f aca="false">I13*J13</f>
+      <c r="K13" s="8">
+        <f t="shared" si="0"/>
         <v>2500</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="n">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A14" s="5">
         <v>13</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="6">
         <v>46060</v>
       </c>
       <c r="C14" s="5" t="s">
@@ -1171,22 +1105,22 @@
       <c r="H14" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="10" t="n">
+      <c r="I14" s="5">
+        <v>1</v>
+      </c>
+      <c r="J14" s="10">
         <v>3700</v>
       </c>
-      <c r="K14" s="8" t="n">
-        <f aca="false">I14*J14</f>
+      <c r="K14" s="8">
+        <f t="shared" si="0"/>
         <v>3700</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="6" t="n">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A15" s="5">
+        <v>14</v>
+      </c>
+      <c r="B15" s="6">
         <v>46060</v>
       </c>
       <c r="C15" s="5" t="s">
@@ -1207,22 +1141,22 @@
       <c r="H15" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" s="9" t="n">
+      <c r="I15" s="5">
+        <v>1</v>
+      </c>
+      <c r="J15" s="9">
         <v>3700</v>
       </c>
-      <c r="K15" s="8" t="n">
-        <f aca="false">I15*J15</f>
+      <c r="K15" s="8">
+        <f t="shared" si="0"/>
         <v>3700</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="n">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A16" s="5">
         <v>15</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="6">
         <v>46060</v>
       </c>
       <c r="C16" s="5" t="s">
@@ -1243,22 +1177,22 @@
       <c r="H16" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I16" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" s="7" t="n">
+      <c r="I16" s="5">
+        <v>1</v>
+      </c>
+      <c r="J16" s="7">
         <v>3500</v>
       </c>
-      <c r="K16" s="8" t="n">
-        <f aca="false">I16*J16</f>
+      <c r="K16" s="8">
+        <f t="shared" si="0"/>
         <v>3500</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="6" t="n">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A17" s="5">
+        <v>16</v>
+      </c>
+      <c r="B17" s="6">
         <v>46063</v>
       </c>
       <c r="C17" s="5" t="s">
@@ -1279,22 +1213,22 @@
       <c r="H17" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I17" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" s="7" t="n">
+      <c r="I17" s="5">
+        <v>1</v>
+      </c>
+      <c r="J17" s="7">
         <v>9000</v>
       </c>
-      <c r="K17" s="8" t="n">
-        <f aca="false">I17*J17</f>
+      <c r="K17" s="8">
+        <f t="shared" si="0"/>
         <v>9000</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="n">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A18" s="5">
         <v>17</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="6">
         <v>46063</v>
       </c>
       <c r="C18" s="5" t="s">
@@ -1315,22 +1249,22 @@
       <c r="H18" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I18" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="9" t="n">
+      <c r="I18" s="5">
+        <v>1</v>
+      </c>
+      <c r="J18" s="9">
         <v>4500</v>
       </c>
-      <c r="K18" s="8" t="n">
-        <f aca="false">I18*J18</f>
+      <c r="K18" s="8">
+        <f t="shared" si="0"/>
         <v>4500</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="n">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A19" s="5">
         <v>18</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="6">
         <v>46063</v>
       </c>
       <c r="C19" s="5" t="s">
@@ -1351,22 +1285,22 @@
       <c r="H19" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I19" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" s="10" t="n">
+      <c r="I19" s="5">
+        <v>1</v>
+      </c>
+      <c r="J19" s="10">
         <v>9000</v>
       </c>
-      <c r="K19" s="8" t="n">
-        <f aca="false">I19*J19</f>
+      <c r="K19" s="8">
+        <f t="shared" si="0"/>
         <v>9000</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="n">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A20" s="5">
         <v>19</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="6">
         <v>46063</v>
       </c>
       <c r="C20" s="5" t="s">
@@ -1387,22 +1321,22 @@
       <c r="H20" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I20" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" s="10" t="n">
+      <c r="I20" s="5">
+        <v>1</v>
+      </c>
+      <c r="J20" s="10">
         <v>3700</v>
       </c>
-      <c r="K20" s="8" t="n">
-        <f aca="false">I20*J20</f>
+      <c r="K20" s="8">
+        <f t="shared" si="0"/>
         <v>3700</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5" t="n">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A21" s="5">
         <v>20</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="6">
         <v>46083</v>
       </c>
       <c r="C21" s="5" t="s">
@@ -1423,22 +1357,22 @@
       <c r="H21" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I21" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" s="9" t="n">
+      <c r="I21" s="5">
+        <v>1</v>
+      </c>
+      <c r="J21" s="9">
         <v>4500</v>
       </c>
-      <c r="K21" s="8" t="n">
-        <f aca="false">I21*J21</f>
+      <c r="K21" s="8">
+        <f t="shared" si="0"/>
         <v>4500</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="n">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A22" s="5">
         <v>21</v>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="6">
         <v>46083</v>
       </c>
       <c r="C22" s="5" t="s">
@@ -1459,22 +1393,22 @@
       <c r="H22" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I22" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" s="7" t="n">
+      <c r="I22" s="5">
+        <v>1</v>
+      </c>
+      <c r="J22" s="7">
         <v>3000</v>
       </c>
-      <c r="K22" s="8" t="n">
-        <f aca="false">I22*J22</f>
+      <c r="K22" s="8">
+        <f t="shared" si="0"/>
         <v>3000</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="n">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A23" s="5">
         <v>22</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="6">
         <v>46083</v>
       </c>
       <c r="C23" s="5" t="s">
@@ -1495,22 +1429,22 @@
       <c r="H23" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I23" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" s="8" t="n">
+      <c r="I23" s="5">
+        <v>1</v>
+      </c>
+      <c r="J23" s="8">
         <v>3000</v>
       </c>
-      <c r="K23" s="8" t="n">
-        <f aca="false">I23*J23</f>
+      <c r="K23" s="8">
+        <f t="shared" si="0"/>
         <v>3000</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="5" t="n">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A24" s="5">
         <v>23</v>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B24" s="6">
         <v>46083</v>
       </c>
       <c r="C24" s="5" t="s">
@@ -1531,22 +1465,22 @@
       <c r="H24" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I24" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" s="8" t="n">
+      <c r="I24" s="5">
+        <v>1</v>
+      </c>
+      <c r="J24" s="8">
         <v>2900</v>
       </c>
-      <c r="K24" s="8" t="n">
-        <f aca="false">I24*J24</f>
+      <c r="K24" s="8">
+        <f t="shared" si="0"/>
         <v>2900</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="n">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A25" s="5">
         <v>24</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="6">
         <v>46083</v>
       </c>
       <c r="C25" s="5" t="s">
@@ -1567,22 +1501,22 @@
       <c r="H25" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I25" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" s="9" t="n">
+      <c r="I25" s="5">
+        <v>1</v>
+      </c>
+      <c r="J25" s="9">
         <v>3500</v>
       </c>
-      <c r="K25" s="8" t="n">
-        <f aca="false">I25*J25</f>
+      <c r="K25" s="8">
+        <f t="shared" si="0"/>
         <v>3500</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="5" t="n">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A26" s="5">
         <v>25</v>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="6">
         <v>46083</v>
       </c>
       <c r="C26" s="5" t="s">
@@ -1603,22 +1537,22 @@
       <c r="H26" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I26" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" s="7" t="n">
+      <c r="I26" s="5">
+        <v>1</v>
+      </c>
+      <c r="J26" s="7">
         <v>3500</v>
       </c>
-      <c r="K26" s="8" t="n">
-        <f aca="false">I26*J26</f>
+      <c r="K26" s="8">
+        <f t="shared" si="0"/>
         <v>3500</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="5" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="6" t="n">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A27" s="5">
+        <v>26</v>
+      </c>
+      <c r="B27" s="6">
         <v>46083</v>
       </c>
       <c r="C27" s="5" t="s">
@@ -1639,22 +1573,22 @@
       <c r="H27" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" s="9" t="n">
+      <c r="I27" s="5">
+        <v>1</v>
+      </c>
+      <c r="J27" s="9">
         <v>3700</v>
       </c>
-      <c r="K27" s="8" t="n">
-        <f aca="false">I27*J27</f>
+      <c r="K27" s="8">
+        <f t="shared" si="0"/>
         <v>3700</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="5" t="n">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A28" s="5">
         <v>27</v>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="6">
         <v>46083</v>
       </c>
       <c r="C28" s="5" t="s">
@@ -1675,22 +1609,22 @@
       <c r="H28" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I28" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" s="10" t="n">
+      <c r="I28" s="5">
+        <v>1</v>
+      </c>
+      <c r="J28" s="10">
         <v>3700</v>
       </c>
-      <c r="K28" s="8" t="n">
-        <f aca="false">I28*J28</f>
+      <c r="K28" s="8">
+        <f t="shared" si="0"/>
         <v>3700</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5" t="n">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A29" s="5">
         <v>28</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="6">
         <v>46083</v>
       </c>
       <c r="C29" s="5" t="s">
@@ -1711,22 +1645,22 @@
       <c r="H29" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I29" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" s="10" t="n">
+      <c r="I29" s="5">
+        <v>1</v>
+      </c>
+      <c r="J29" s="10">
         <v>9500</v>
       </c>
-      <c r="K29" s="8" t="n">
-        <f aca="false">I29*J29</f>
+      <c r="K29" s="8">
+        <f t="shared" si="0"/>
         <v>9500</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="5" t="n">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A30" s="5">
         <v>29</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="6">
         <v>46083</v>
       </c>
       <c r="C30" s="5" t="s">
@@ -1747,22 +1681,22 @@
       <c r="H30" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I30" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" s="8" t="n">
+      <c r="I30" s="5">
+        <v>1</v>
+      </c>
+      <c r="J30" s="8">
         <v>1551.72</v>
       </c>
-      <c r="K30" s="8" t="n">
-        <f aca="false">I30*J30</f>
+      <c r="K30" s="8">
+        <f t="shared" si="0"/>
         <v>1551.72</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5" t="n">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A31" s="5">
         <v>30</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="6">
         <v>46083</v>
       </c>
       <c r="C31" s="5" t="s">
@@ -1783,22 +1717,22 @@
       <c r="H31" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" s="8" t="n">
-        <v>1293.1</v>
-      </c>
-      <c r="K31" s="8" t="n">
-        <f aca="false">I31*J31</f>
-        <v>1293.1</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="5" t="n">
+      <c r="I31" s="5">
+        <v>1</v>
+      </c>
+      <c r="J31" s="8">
+        <v>1293.0999999999999</v>
+      </c>
+      <c r="K31" s="8">
+        <f t="shared" si="0"/>
+        <v>1293.0999999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A32" s="5">
         <v>31</v>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="6">
         <v>46083</v>
       </c>
       <c r="C32" s="5" t="s">
@@ -1819,22 +1753,22 @@
       <c r="H32" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I32" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" s="8" t="n">
+      <c r="I32" s="5">
+        <v>1</v>
+      </c>
+      <c r="J32" s="8">
         <v>18965.52</v>
       </c>
-      <c r="K32" s="8" t="n">
-        <f aca="false">I32*J32</f>
+      <c r="K32" s="8">
+        <f t="shared" si="0"/>
         <v>18965.52</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="5" t="n">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A33" s="5">
         <v>32</v>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="6">
         <v>46083</v>
       </c>
       <c r="C33" s="5" t="s">
@@ -1855,22 +1789,22 @@
       <c r="H33" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I33" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" s="8" t="n">
+      <c r="I33" s="5">
+        <v>1</v>
+      </c>
+      <c r="J33" s="8">
         <v>172.41</v>
       </c>
-      <c r="K33" s="8" t="n">
-        <f aca="false">I33*J33</f>
+      <c r="K33" s="8">
+        <f t="shared" si="0"/>
         <v>172.41</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="5" t="n">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A34" s="5">
         <v>33</v>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="6">
         <v>46091</v>
       </c>
       <c r="C34" s="5" t="s">
@@ -1891,22 +1825,22 @@
       <c r="H34" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I34" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" s="8" t="n">
+      <c r="I34" s="5">
+        <v>1</v>
+      </c>
+      <c r="J34" s="8">
         <v>2800</v>
       </c>
-      <c r="K34" s="8" t="n">
-        <f aca="false">I34*J34</f>
+      <c r="K34" s="8">
+        <f t="shared" ref="K34:K65" si="1">I34*J34</f>
         <v>2800</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="5" t="n">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A35" s="5">
         <v>34</v>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="6">
         <v>46091</v>
       </c>
       <c r="C35" s="5" t="s">
@@ -1927,22 +1861,22 @@
       <c r="H35" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I35" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" s="8" t="n">
+      <c r="I35" s="5">
+        <v>1</v>
+      </c>
+      <c r="J35" s="8">
         <v>300</v>
       </c>
-      <c r="K35" s="8" t="n">
-        <f aca="false">I35*J35</f>
+      <c r="K35" s="8">
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="5" t="n">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A36" s="5">
         <v>35</v>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B36" s="6">
         <v>46091</v>
       </c>
       <c r="C36" s="5" t="s">
@@ -1963,22 +1897,22 @@
       <c r="H36" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I36" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" s="8" t="n">
+      <c r="I36" s="5">
+        <v>1</v>
+      </c>
+      <c r="J36" s="8">
         <v>300</v>
       </c>
-      <c r="K36" s="8" t="n">
-        <f aca="false">I36*J36</f>
+      <c r="K36" s="8">
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="5" t="n">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A37" s="5">
         <v>36</v>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B37" s="6">
         <v>46091</v>
       </c>
       <c r="C37" s="5" t="s">
@@ -1999,22 +1933,22 @@
       <c r="H37" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I37" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" s="8" t="n">
+      <c r="I37" s="5">
+        <v>1</v>
+      </c>
+      <c r="J37" s="8">
         <v>300</v>
       </c>
-      <c r="K37" s="8" t="n">
-        <f aca="false">I37*J37</f>
+      <c r="K37" s="8">
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="5" t="n">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A38" s="5">
         <v>37</v>
       </c>
-      <c r="B38" s="6" t="n">
+      <c r="B38" s="6">
         <v>46091</v>
       </c>
       <c r="C38" s="5" t="s">
@@ -2035,22 +1969,22 @@
       <c r="H38" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I38" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" s="8" t="n">
+      <c r="I38" s="5">
+        <v>1</v>
+      </c>
+      <c r="J38" s="8">
         <v>300</v>
       </c>
-      <c r="K38" s="8" t="n">
-        <f aca="false">I38*J38</f>
+      <c r="K38" s="8">
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="5" t="n">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A39" s="5">
         <v>38</v>
       </c>
-      <c r="B39" s="6" t="n">
+      <c r="B39" s="6">
         <v>46091</v>
       </c>
       <c r="C39" s="5" t="s">
@@ -2071,22 +2005,22 @@
       <c r="H39" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I39" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" s="8" t="n">
+      <c r="I39" s="5">
+        <v>1</v>
+      </c>
+      <c r="J39" s="8">
         <v>300</v>
       </c>
-      <c r="K39" s="8" t="n">
-        <f aca="false">I39*J39</f>
+      <c r="K39" s="8">
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="5" t="n">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A40" s="5">
         <v>39</v>
       </c>
-      <c r="B40" s="6" t="n">
+      <c r="B40" s="6">
         <v>46091</v>
       </c>
       <c r="C40" s="5" t="s">
@@ -2107,22 +2041,22 @@
       <c r="H40" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I40" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" s="8" t="n">
+      <c r="I40" s="5">
+        <v>1</v>
+      </c>
+      <c r="J40" s="8">
         <v>300</v>
       </c>
-      <c r="K40" s="8" t="n">
-        <f aca="false">I40*J40</f>
+      <c r="K40" s="8">
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="5" t="n">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A41" s="5">
         <v>40</v>
       </c>
-      <c r="B41" s="6" t="n">
+      <c r="B41" s="6">
         <v>46091</v>
       </c>
       <c r="C41" s="5" t="s">
@@ -2143,22 +2077,22 @@
       <c r="H41" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I41" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J41" s="8" t="n">
+      <c r="I41" s="5">
+        <v>1</v>
+      </c>
+      <c r="J41" s="8">
         <v>300</v>
       </c>
-      <c r="K41" s="8" t="n">
-        <f aca="false">I41*J41</f>
+      <c r="K41" s="8">
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="5" t="n">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A42" s="5">
         <v>41</v>
       </c>
-      <c r="B42" s="6" t="n">
+      <c r="B42" s="6">
         <v>46091</v>
       </c>
       <c r="C42" s="5" t="s">
@@ -2179,22 +2113,22 @@
       <c r="H42" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I42" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J42" s="8" t="n">
+      <c r="I42" s="5">
+        <v>1</v>
+      </c>
+      <c r="J42" s="8">
         <v>900</v>
       </c>
-      <c r="K42" s="8" t="n">
-        <f aca="false">I42*J42</f>
+      <c r="K42" s="8">
+        <f t="shared" si="1"/>
         <v>900</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="5" t="n">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A43" s="5">
         <v>42</v>
       </c>
-      <c r="B43" s="6" t="n">
+      <c r="B43" s="6">
         <v>46091</v>
       </c>
       <c r="C43" s="5" t="s">
@@ -2215,22 +2149,22 @@
       <c r="H43" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I43" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" s="8" t="n">
+      <c r="I43" s="5">
+        <v>1</v>
+      </c>
+      <c r="J43" s="8">
         <v>300</v>
       </c>
-      <c r="K43" s="8" t="n">
-        <f aca="false">I43*J43</f>
+      <c r="K43" s="8">
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="5" t="n">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A44" s="5">
         <v>43</v>
       </c>
-      <c r="B44" s="6" t="n">
+      <c r="B44" s="6">
         <v>46091</v>
       </c>
       <c r="C44" s="5" t="s">
@@ -2251,22 +2185,22 @@
       <c r="H44" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I44" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J44" s="8" t="n">
+      <c r="I44" s="5">
+        <v>1</v>
+      </c>
+      <c r="J44" s="8">
         <v>300</v>
       </c>
-      <c r="K44" s="8" t="n">
-        <f aca="false">I44*J44</f>
+      <c r="K44" s="8">
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="5" t="n">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A45" s="5">
         <v>44</v>
       </c>
-      <c r="B45" s="6" t="n">
+      <c r="B45" s="6">
         <v>46091</v>
       </c>
       <c r="C45" s="5" t="s">
@@ -2287,22 +2221,22 @@
       <c r="H45" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I45" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" s="8" t="n">
+      <c r="I45" s="5">
+        <v>1</v>
+      </c>
+      <c r="J45" s="8">
         <v>400</v>
       </c>
-      <c r="K45" s="8" t="n">
-        <f aca="false">I45*J45</f>
+      <c r="K45" s="8">
+        <f t="shared" si="1"/>
         <v>400</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="5" t="n">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A46" s="5">
         <v>45</v>
       </c>
-      <c r="B46" s="6" t="n">
+      <c r="B46" s="6">
         <v>46091</v>
       </c>
       <c r="C46" s="5" t="s">
@@ -2323,22 +2257,22 @@
       <c r="H46" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I46" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J46" s="8" t="n">
+      <c r="I46" s="5">
+        <v>1</v>
+      </c>
+      <c r="J46" s="8">
         <v>1000</v>
       </c>
-      <c r="K46" s="8" t="n">
-        <f aca="false">I46*J46</f>
+      <c r="K46" s="8">
+        <f t="shared" si="1"/>
         <v>1000</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="5" t="n">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A47" s="5">
         <v>46</v>
       </c>
-      <c r="B47" s="6" t="n">
+      <c r="B47" s="6">
         <v>46091</v>
       </c>
       <c r="C47" s="5" t="s">
@@ -2359,22 +2293,22 @@
       <c r="H47" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I47" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J47" s="8" t="n">
+      <c r="I47" s="5">
+        <v>1</v>
+      </c>
+      <c r="J47" s="8">
         <v>4200</v>
       </c>
-      <c r="K47" s="8" t="n">
-        <f aca="false">I47*J47</f>
+      <c r="K47" s="8">
+        <f t="shared" si="1"/>
         <v>4200</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="5" t="n">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A48" s="5">
         <v>47</v>
       </c>
-      <c r="B48" s="6" t="n">
+      <c r="B48" s="6">
         <v>46091</v>
       </c>
       <c r="C48" s="5" t="s">
@@ -2395,22 +2329,22 @@
       <c r="H48" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I48" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" s="8" t="n">
+      <c r="I48" s="5">
+        <v>1</v>
+      </c>
+      <c r="J48" s="8">
         <v>2450</v>
       </c>
-      <c r="K48" s="8" t="n">
-        <f aca="false">I48*J48</f>
+      <c r="K48" s="8">
+        <f t="shared" si="1"/>
         <v>2450</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="5" t="n">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A49" s="5">
         <v>48</v>
       </c>
-      <c r="B49" s="6" t="n">
+      <c r="B49" s="6">
         <v>46091</v>
       </c>
       <c r="C49" s="5" t="s">
@@ -2431,22 +2365,22 @@
       <c r="H49" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I49" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J49" s="8" t="n">
+      <c r="I49" s="5">
+        <v>1</v>
+      </c>
+      <c r="J49" s="8">
         <v>700</v>
       </c>
-      <c r="K49" s="8" t="n">
-        <f aca="false">I49*J49</f>
+      <c r="K49" s="8">
+        <f t="shared" si="1"/>
         <v>700</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="5" t="n">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A50" s="5">
         <v>49</v>
       </c>
-      <c r="B50" s="6" t="n">
+      <c r="B50" s="6">
         <v>46091</v>
       </c>
       <c r="C50" s="5" t="s">
@@ -2467,22 +2401,22 @@
       <c r="H50" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I50" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J50" s="8" t="n">
+      <c r="I50" s="5">
+        <v>1</v>
+      </c>
+      <c r="J50" s="8">
         <v>1200</v>
       </c>
-      <c r="K50" s="8" t="n">
-        <f aca="false">I50*J50</f>
+      <c r="K50" s="8">
+        <f t="shared" si="1"/>
         <v>1200</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="5" t="n">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A51" s="5">
         <v>50</v>
       </c>
-      <c r="B51" s="6" t="n">
+      <c r="B51" s="6">
         <v>46091</v>
       </c>
       <c r="C51" s="5" t="s">
@@ -2503,22 +2437,22 @@
       <c r="H51" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I51" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J51" s="8" t="n">
+      <c r="I51" s="5">
+        <v>1</v>
+      </c>
+      <c r="J51" s="8">
         <v>600</v>
       </c>
-      <c r="K51" s="8" t="n">
-        <f aca="false">I51*J51</f>
+      <c r="K51" s="8">
+        <f t="shared" si="1"/>
         <v>600</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="5" t="n">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A52" s="5">
         <v>51</v>
       </c>
-      <c r="B52" s="6" t="n">
+      <c r="B52" s="6">
         <v>45732</v>
       </c>
       <c r="C52" s="5" t="s">
@@ -2539,22 +2473,22 @@
       <c r="H52" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I52" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J52" s="9" t="n">
+      <c r="I52" s="5">
+        <v>1</v>
+      </c>
+      <c r="J52" s="9">
         <v>4500</v>
       </c>
-      <c r="K52" s="8" t="n">
-        <f aca="false">I52*J52</f>
+      <c r="K52" s="8">
+        <f t="shared" si="1"/>
         <v>4500</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="5" t="n">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A53" s="5">
         <v>52</v>
       </c>
-      <c r="B53" s="6" t="n">
+      <c r="B53" s="6">
         <v>45732</v>
       </c>
       <c r="C53" s="5" t="s">
@@ -2575,22 +2509,22 @@
       <c r="H53" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I53" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J53" s="7" t="n">
+      <c r="I53" s="5">
+        <v>1</v>
+      </c>
+      <c r="J53" s="7">
         <v>3000</v>
       </c>
-      <c r="K53" s="8" t="n">
-        <f aca="false">I53*J53</f>
+      <c r="K53" s="8">
+        <f t="shared" si="1"/>
         <v>3000</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="5" t="n">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A54" s="5">
         <v>53</v>
       </c>
-      <c r="B54" s="6" t="n">
+      <c r="B54" s="6">
         <v>45732</v>
       </c>
       <c r="C54" s="5" t="s">
@@ -2611,22 +2545,22 @@
       <c r="H54" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I54" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" s="8" t="n">
+      <c r="I54" s="5">
+        <v>1</v>
+      </c>
+      <c r="J54" s="8">
         <v>3000</v>
       </c>
-      <c r="K54" s="8" t="n">
-        <f aca="false">I54*J54</f>
+      <c r="K54" s="8">
+        <f t="shared" si="1"/>
         <v>3000</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="5" t="n">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A55" s="5">
         <v>54</v>
       </c>
-      <c r="B55" s="6" t="n">
+      <c r="B55" s="6">
         <v>45732</v>
       </c>
       <c r="C55" s="5" t="s">
@@ -2647,22 +2581,22 @@
       <c r="H55" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I55" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J55" s="8" t="n">
+      <c r="I55" s="5">
+        <v>1</v>
+      </c>
+      <c r="J55" s="8">
         <v>2900</v>
       </c>
-      <c r="K55" s="8" t="n">
-        <f aca="false">I55*J55</f>
+      <c r="K55" s="8">
+        <f t="shared" si="1"/>
         <v>2900</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="5" t="n">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A56" s="5">
         <v>55</v>
       </c>
-      <c r="B56" s="6" t="n">
+      <c r="B56" s="6">
         <v>45732</v>
       </c>
       <c r="C56" s="5" t="s">
@@ -2683,22 +2617,22 @@
       <c r="H56" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I56" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J56" s="9" t="n">
+      <c r="I56" s="5">
+        <v>1</v>
+      </c>
+      <c r="J56" s="9">
         <v>3500</v>
       </c>
-      <c r="K56" s="8" t="n">
-        <f aca="false">I56*J56</f>
+      <c r="K56" s="8">
+        <f t="shared" si="1"/>
         <v>3500</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="5" t="n">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A57" s="5">
         <v>56</v>
       </c>
-      <c r="B57" s="6" t="n">
+      <c r="B57" s="6">
         <v>45732</v>
       </c>
       <c r="C57" s="5" t="s">
@@ -2719,22 +2653,22 @@
       <c r="H57" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I57" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J57" s="7" t="n">
+      <c r="I57" s="5">
+        <v>1</v>
+      </c>
+      <c r="J57" s="7">
         <v>3500</v>
       </c>
-      <c r="K57" s="8" t="n">
-        <f aca="false">I57*J57</f>
+      <c r="K57" s="8">
+        <f t="shared" si="1"/>
         <v>3500</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="5" t="n">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A58" s="5">
         <v>57</v>
       </c>
-      <c r="B58" s="6" t="n">
+      <c r="B58" s="6">
         <v>45732</v>
       </c>
       <c r="C58" s="5" t="s">
@@ -2755,22 +2689,22 @@
       <c r="H58" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I58" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J58" s="9" t="n">
+      <c r="I58" s="5">
+        <v>1</v>
+      </c>
+      <c r="J58" s="9">
         <v>3700</v>
       </c>
-      <c r="K58" s="8" t="n">
-        <f aca="false">I58*J58</f>
+      <c r="K58" s="8">
+        <f t="shared" si="1"/>
         <v>3700</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="5" t="n">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A59" s="5">
         <v>58</v>
       </c>
-      <c r="B59" s="6" t="n">
+      <c r="B59" s="6">
         <v>45732</v>
       </c>
       <c r="C59" s="5" t="s">
@@ -2791,22 +2725,22 @@
       <c r="H59" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I59" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J59" s="10" t="n">
+      <c r="I59" s="5">
+        <v>1</v>
+      </c>
+      <c r="J59" s="10">
         <v>3700</v>
       </c>
-      <c r="K59" s="8" t="n">
-        <f aca="false">I59*J59</f>
+      <c r="K59" s="8">
+        <f t="shared" si="1"/>
         <v>3700</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="5" t="n">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A60" s="5">
         <v>59</v>
       </c>
-      <c r="B60" s="6" t="n">
+      <c r="B60" s="6">
         <v>45732</v>
       </c>
       <c r="C60" s="5" t="s">
@@ -2827,22 +2761,22 @@
       <c r="H60" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I60" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J60" s="10" t="n">
+      <c r="I60" s="5">
+        <v>1</v>
+      </c>
+      <c r="J60" s="10">
         <v>9500</v>
       </c>
-      <c r="K60" s="8" t="n">
-        <f aca="false">I60*J60</f>
+      <c r="K60" s="8">
+        <f t="shared" si="1"/>
         <v>9500</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="5" t="n">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A61" s="5">
         <v>60</v>
       </c>
-      <c r="B61" s="6" t="n">
+      <c r="B61" s="6">
         <v>45735</v>
       </c>
       <c r="C61" s="5" t="s">
@@ -2863,22 +2797,22 @@
       <c r="H61" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I61" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J61" s="8" t="n">
+      <c r="I61" s="5">
+        <v>1</v>
+      </c>
+      <c r="J61" s="8">
         <v>2800</v>
       </c>
-      <c r="K61" s="8" t="n">
-        <f aca="false">I61*J61</f>
+      <c r="K61" s="8">
+        <f t="shared" si="1"/>
         <v>2800</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="5" t="n">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A62" s="5">
         <v>61</v>
       </c>
-      <c r="B62" s="6" t="n">
+      <c r="B62" s="6">
         <v>45735</v>
       </c>
       <c r="C62" s="5" t="s">
@@ -2899,22 +2833,22 @@
       <c r="H62" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I62" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J62" s="8" t="n">
+      <c r="I62" s="5">
+        <v>1</v>
+      </c>
+      <c r="J62" s="8">
         <v>300</v>
       </c>
-      <c r="K62" s="8" t="n">
-        <f aca="false">I62*J62</f>
+      <c r="K62" s="8">
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="5" t="n">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A63" s="5">
         <v>62</v>
       </c>
-      <c r="B63" s="6" t="n">
+      <c r="B63" s="6">
         <v>45735</v>
       </c>
       <c r="C63" s="5" t="s">
@@ -2935,22 +2869,22 @@
       <c r="H63" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I63" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J63" s="8" t="n">
+      <c r="I63" s="5">
+        <v>1</v>
+      </c>
+      <c r="J63" s="8">
         <v>150</v>
       </c>
-      <c r="K63" s="8" t="n">
-        <f aca="false">I63*J63</f>
+      <c r="K63" s="8">
+        <f t="shared" si="1"/>
         <v>150</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="5" t="n">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A64" s="5">
         <v>63</v>
       </c>
-      <c r="B64" s="6" t="n">
+      <c r="B64" s="6">
         <v>45735</v>
       </c>
       <c r="C64" s="5" t="s">
@@ -2971,22 +2905,22 @@
       <c r="H64" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I64" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J64" s="8" t="n">
+      <c r="I64" s="5">
+        <v>1</v>
+      </c>
+      <c r="J64" s="8">
         <v>300</v>
       </c>
-      <c r="K64" s="8" t="n">
-        <f aca="false">I64*J64</f>
+      <c r="K64" s="8">
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="5" t="n">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A65" s="5">
         <v>64</v>
       </c>
-      <c r="B65" s="6" t="n">
+      <c r="B65" s="6">
         <v>45735</v>
       </c>
       <c r="C65" s="5" t="s">
@@ -3007,22 +2941,22 @@
       <c r="H65" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I65" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J65" s="8" t="n">
+      <c r="I65" s="5">
+        <v>1</v>
+      </c>
+      <c r="J65" s="8">
         <v>300</v>
       </c>
-      <c r="K65" s="8" t="n">
-        <f aca="false">I65*J65</f>
+      <c r="K65" s="8">
+        <f t="shared" si="1"/>
         <v>300</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="5" t="n">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A66" s="5">
         <v>65</v>
       </c>
-      <c r="B66" s="6" t="n">
+      <c r="B66" s="6">
         <v>45735</v>
       </c>
       <c r="C66" s="5" t="s">
@@ -3043,22 +2977,22 @@
       <c r="H66" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I66" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J66" s="8" t="n">
+      <c r="I66" s="5">
+        <v>1</v>
+      </c>
+      <c r="J66" s="8">
         <v>300</v>
       </c>
-      <c r="K66" s="8" t="n">
-        <f aca="false">I66*J66</f>
+      <c r="K66" s="8">
+        <f t="shared" ref="K66:K97" si="2">I66*J66</f>
         <v>300</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="5" t="n">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A67" s="5">
         <v>66</v>
       </c>
-      <c r="B67" s="6" t="n">
+      <c r="B67" s="6">
         <v>45735</v>
       </c>
       <c r="C67" s="5" t="s">
@@ -3079,22 +3013,22 @@
       <c r="H67" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I67" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J67" s="8" t="n">
+      <c r="I67" s="5">
+        <v>1</v>
+      </c>
+      <c r="J67" s="8">
         <v>300</v>
       </c>
-      <c r="K67" s="8" t="n">
-        <f aca="false">I67*J67</f>
+      <c r="K67" s="8">
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="5" t="n">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A68" s="5">
         <v>67</v>
       </c>
-      <c r="B68" s="6" t="n">
+      <c r="B68" s="6">
         <v>45735</v>
       </c>
       <c r="C68" s="5" t="s">
@@ -3115,22 +3049,22 @@
       <c r="H68" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I68" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J68" s="8" t="n">
+      <c r="I68" s="5">
+        <v>1</v>
+      </c>
+      <c r="J68" s="8">
         <v>300</v>
       </c>
-      <c r="K68" s="8" t="n">
-        <f aca="false">I68*J68</f>
+      <c r="K68" s="8">
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="5" t="n">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A69" s="5">
         <v>68</v>
       </c>
-      <c r="B69" s="6" t="n">
+      <c r="B69" s="6">
         <v>45735</v>
       </c>
       <c r="C69" s="5" t="s">
@@ -3151,22 +3085,22 @@
       <c r="H69" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I69" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J69" s="8" t="n">
+      <c r="I69" s="5">
+        <v>1</v>
+      </c>
+      <c r="J69" s="8">
         <v>350</v>
       </c>
-      <c r="K69" s="8" t="n">
-        <f aca="false">I69*J69</f>
+      <c r="K69" s="8">
+        <f t="shared" si="2"/>
         <v>350</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="5" t="n">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A70" s="5">
         <v>69</v>
       </c>
-      <c r="B70" s="6" t="n">
+      <c r="B70" s="6">
         <v>45735</v>
       </c>
       <c r="C70" s="5" t="s">
@@ -3187,22 +3121,22 @@
       <c r="H70" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I70" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J70" s="8" t="n">
+      <c r="I70" s="5">
+        <v>1</v>
+      </c>
+      <c r="J70" s="8">
         <v>350</v>
       </c>
-      <c r="K70" s="8" t="n">
-        <f aca="false">I70*J70</f>
+      <c r="K70" s="8">
+        <f t="shared" si="2"/>
         <v>350</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="5" t="n">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A71" s="5">
         <v>70</v>
       </c>
-      <c r="B71" s="6" t="n">
+      <c r="B71" s="6">
         <v>45735</v>
       </c>
       <c r="C71" s="5" t="s">
@@ -3223,22 +3157,22 @@
       <c r="H71" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I71" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J71" s="8" t="n">
+      <c r="I71" s="5">
+        <v>1</v>
+      </c>
+      <c r="J71" s="8">
         <v>300</v>
       </c>
-      <c r="K71" s="8" t="n">
-        <f aca="false">I71*J71</f>
+      <c r="K71" s="8">
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="5" t="n">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A72" s="5">
         <v>71</v>
       </c>
-      <c r="B72" s="6" t="n">
+      <c r="B72" s="6">
         <v>45735</v>
       </c>
       <c r="C72" s="5" t="s">
@@ -3259,22 +3193,22 @@
       <c r="H72" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I72" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J72" s="8" t="n">
+      <c r="I72" s="5">
+        <v>1</v>
+      </c>
+      <c r="J72" s="8">
         <v>400</v>
       </c>
-      <c r="K72" s="8" t="n">
-        <f aca="false">I72*J72</f>
+      <c r="K72" s="8">
+        <f t="shared" si="2"/>
         <v>400</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="5" t="n">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A73" s="5">
         <v>72</v>
       </c>
-      <c r="B73" s="6" t="n">
+      <c r="B73" s="6">
         <v>45735</v>
       </c>
       <c r="C73" s="5" t="s">
@@ -3295,22 +3229,22 @@
       <c r="H73" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I73" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J73" s="8" t="n">
+      <c r="I73" s="5">
+        <v>1</v>
+      </c>
+      <c r="J73" s="8">
         <v>1200</v>
       </c>
-      <c r="K73" s="8" t="n">
-        <f aca="false">I73*J73</f>
+      <c r="K73" s="8">
+        <f t="shared" si="2"/>
         <v>1200</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="5" t="n">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A74" s="5">
         <v>73</v>
       </c>
-      <c r="B74" s="6" t="n">
+      <c r="B74" s="6">
         <v>45735</v>
       </c>
       <c r="C74" s="5" t="s">
@@ -3331,22 +3265,22 @@
       <c r="H74" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I74" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J74" s="8" t="n">
+      <c r="I74" s="5">
+        <v>1</v>
+      </c>
+      <c r="J74" s="8">
         <v>4200</v>
       </c>
-      <c r="K74" s="8" t="n">
-        <f aca="false">I74*J74</f>
+      <c r="K74" s="8">
+        <f t="shared" si="2"/>
         <v>4200</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="5" t="n">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A75" s="5">
         <v>74</v>
       </c>
-      <c r="B75" s="6" t="n">
+      <c r="B75" s="6">
         <v>45735</v>
       </c>
       <c r="C75" s="5" t="s">
@@ -3367,22 +3301,22 @@
       <c r="H75" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I75" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J75" s="8" t="n">
+      <c r="I75" s="5">
+        <v>1</v>
+      </c>
+      <c r="J75" s="8">
         <v>2450</v>
       </c>
-      <c r="K75" s="8" t="n">
-        <f aca="false">I75*J75</f>
+      <c r="K75" s="8">
+        <f t="shared" si="2"/>
         <v>2450</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="5" t="n">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A76" s="5">
         <v>75</v>
       </c>
-      <c r="B76" s="6" t="n">
+      <c r="B76" s="6">
         <v>45735</v>
       </c>
       <c r="C76" s="5" t="s">
@@ -3403,22 +3337,22 @@
       <c r="H76" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I76" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J76" s="8" t="n">
+      <c r="I76" s="5">
+        <v>1</v>
+      </c>
+      <c r="J76" s="8">
         <v>700</v>
       </c>
-      <c r="K76" s="8" t="n">
-        <f aca="false">I76*J76</f>
+      <c r="K76" s="8">
+        <f t="shared" si="2"/>
         <v>700</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="5" t="n">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A77" s="5">
         <v>76</v>
       </c>
-      <c r="B77" s="6" t="n">
+      <c r="B77" s="6">
         <v>45735</v>
       </c>
       <c r="C77" s="5" t="s">
@@ -3439,22 +3373,22 @@
       <c r="H77" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I77" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J77" s="8" t="n">
+      <c r="I77" s="5">
+        <v>1</v>
+      </c>
+      <c r="J77" s="8">
         <v>600</v>
       </c>
-      <c r="K77" s="8" t="n">
-        <f aca="false">I77*J77</f>
+      <c r="K77" s="8">
+        <f t="shared" si="2"/>
         <v>600</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="5" t="n">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A78" s="5">
         <v>77</v>
       </c>
-      <c r="B78" s="6" t="n">
+      <c r="B78" s="6">
         <v>45735</v>
       </c>
       <c r="C78" s="5" t="s">
@@ -3475,22 +3409,22 @@
       <c r="H78" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I78" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J78" s="8" t="n">
+      <c r="I78" s="5">
+        <v>1</v>
+      </c>
+      <c r="J78" s="8">
         <v>600</v>
       </c>
-      <c r="K78" s="8" t="n">
-        <f aca="false">I78*J78</f>
+      <c r="K78" s="8">
+        <f t="shared" si="2"/>
         <v>600</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="5" t="n">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A79" s="5">
         <v>78</v>
       </c>
-      <c r="B79" s="6" t="n">
+      <c r="B79" s="6">
         <v>46100</v>
       </c>
       <c r="C79" s="5" t="s">
@@ -3511,22 +3445,22 @@
       <c r="H79" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I79" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J79" s="8" t="n">
+      <c r="I79" s="5">
+        <v>1</v>
+      </c>
+      <c r="J79" s="8">
         <v>18965.52</v>
       </c>
-      <c r="K79" s="8" t="n">
-        <f aca="false">I79*J79</f>
+      <c r="K79" s="8">
+        <f t="shared" si="2"/>
         <v>18965.52</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="5" t="n">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A80" s="5">
         <v>79</v>
       </c>
-      <c r="B80" s="6" t="n">
+      <c r="B80" s="6">
         <v>46100</v>
       </c>
       <c r="C80" s="5" t="s">
@@ -3547,19 +3481,19 @@
       <c r="H80" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="I80" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J80" s="8" t="n">
+      <c r="I80" s="5">
+        <v>1</v>
+      </c>
+      <c r="J80" s="8">
         <v>172.41</v>
       </c>
-      <c r="K80" s="8" t="n">
-        <f aca="false">I80*J80</f>
+      <c r="K80" s="8">
+        <f t="shared" si="2"/>
         <v>172.41</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="5" t="n">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A81" s="5">
         <v>81</v>
       </c>
       <c r="B81" s="5"/>
@@ -3573,8 +3507,8 @@
       <c r="J81" s="8"/>
       <c r="K81" s="8"/>
     </row>
-    <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="5" t="n">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A82" s="5">
         <v>82</v>
       </c>
       <c r="B82" s="5"/>
@@ -3588,8 +3522,8 @@
       <c r="J82" s="8"/>
       <c r="K82" s="8"/>
     </row>
-    <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="5" t="n">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A83" s="5">
         <v>83</v>
       </c>
       <c r="B83" s="5"/>
@@ -3603,8 +3537,8 @@
       <c r="J83" s="8"/>
       <c r="K83" s="8"/>
     </row>
-    <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="5" t="n">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A84" s="5">
         <v>84</v>
       </c>
       <c r="B84" s="5"/>
@@ -3618,8 +3552,8 @@
       <c r="J84" s="8"/>
       <c r="K84" s="8"/>
     </row>
-    <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="5" t="n">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A85" s="5">
         <v>85</v>
       </c>
       <c r="B85" s="5"/>
@@ -3633,8 +3567,8 @@
       <c r="J85" s="8"/>
       <c r="K85" s="8"/>
     </row>
-    <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="5" t="n">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A86" s="5">
         <v>86</v>
       </c>
       <c r="B86" s="5"/>
@@ -3648,8 +3582,8 @@
       <c r="J86" s="8"/>
       <c r="K86" s="8"/>
     </row>
-    <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="5" t="n">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A87" s="5">
         <v>87</v>
       </c>
       <c r="B87" s="5"/>
@@ -3663,8 +3597,8 @@
       <c r="J87" s="8"/>
       <c r="K87" s="8"/>
     </row>
-    <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="5" t="n">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A88" s="5">
         <v>88</v>
       </c>
       <c r="B88" s="5"/>
@@ -3678,8 +3612,8 @@
       <c r="J88" s="8"/>
       <c r="K88" s="8"/>
     </row>
-    <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="5" t="n">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A89" s="5">
         <v>89</v>
       </c>
       <c r="B89" s="5"/>
@@ -3693,8 +3627,8 @@
       <c r="J89" s="8"/>
       <c r="K89" s="8"/>
     </row>
-    <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="5" t="n">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A90" s="5">
         <v>90</v>
       </c>
       <c r="B90" s="5"/>
@@ -3708,8 +3642,8 @@
       <c r="J90" s="8"/>
       <c r="K90" s="8"/>
     </row>
-    <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="5" t="n">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A91" s="5">
         <v>91</v>
       </c>
       <c r="B91" s="5"/>
@@ -3723,8 +3657,8 @@
       <c r="J91" s="8"/>
       <c r="K91" s="8"/>
     </row>
-    <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="5" t="n">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A92" s="5">
         <v>92</v>
       </c>
       <c r="B92" s="5"/>
@@ -3738,8 +3672,8 @@
       <c r="J92" s="8"/>
       <c r="K92" s="8"/>
     </row>
-    <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="5" t="n">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A93" s="5">
         <v>93</v>
       </c>
       <c r="B93" s="5"/>
@@ -3753,8 +3687,8 @@
       <c r="J93" s="8"/>
       <c r="K93" s="8"/>
     </row>
-    <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="5" t="n">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A94" s="5">
         <v>94</v>
       </c>
       <c r="B94" s="5"/>
@@ -3768,8 +3702,8 @@
       <c r="J94" s="8"/>
       <c r="K94" s="8"/>
     </row>
-    <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="5" t="n">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A95" s="5">
         <v>95</v>
       </c>
       <c r="B95" s="5"/>
@@ -3783,8 +3717,8 @@
       <c r="J95" s="8"/>
       <c r="K95" s="8"/>
     </row>
-    <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="5" t="n">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A96" s="5">
         <v>96</v>
       </c>
       <c r="B96" s="5"/>
@@ -3798,8 +3732,8 @@
       <c r="J96" s="8"/>
       <c r="K96" s="8"/>
     </row>
-    <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="5" t="n">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A97" s="5">
         <v>97</v>
       </c>
       <c r="B97" s="5"/>
@@ -3813,8 +3747,8 @@
       <c r="J97" s="8"/>
       <c r="K97" s="8"/>
     </row>
-    <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="5" t="n">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A98" s="5">
         <v>98</v>
       </c>
       <c r="B98" s="5"/>
@@ -3828,8 +3762,8 @@
       <c r="J98" s="8"/>
       <c r="K98" s="8"/>
     </row>
-    <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="5" t="n">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A99" s="5">
         <v>99</v>
       </c>
       <c r="B99" s="5"/>
@@ -3843,8 +3777,8 @@
       <c r="J99" s="8"/>
       <c r="K99" s="8"/>
     </row>
-    <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="5" t="n">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A100" s="5">
         <v>100</v>
       </c>
       <c r="B100" s="5"/>
@@ -3858,8 +3792,8 @@
       <c r="J100" s="8"/>
       <c r="K100" s="8"/>
     </row>
-    <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="5" t="n">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A101" s="5">
         <v>101</v>
       </c>
       <c r="B101" s="5"/>
@@ -3873,8 +3807,8 @@
       <c r="J101" s="8"/>
       <c r="K101" s="8"/>
     </row>
-    <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="5" t="n">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A102" s="5">
         <v>102</v>
       </c>
       <c r="B102" s="5"/>
@@ -3888,8 +3822,8 @@
       <c r="J102" s="8"/>
       <c r="K102" s="8"/>
     </row>
-    <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="5" t="n">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A103" s="5">
         <v>103</v>
       </c>
       <c r="B103" s="5"/>
@@ -3903,8 +3837,8 @@
       <c r="J103" s="8"/>
       <c r="K103" s="8"/>
     </row>
-    <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="5" t="n">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A104" s="5">
         <v>104</v>
       </c>
       <c r="B104" s="5"/>
@@ -3918,8 +3852,8 @@
       <c r="J104" s="8"/>
       <c r="K104" s="8"/>
     </row>
-    <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="5" t="n">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A105" s="5">
         <v>105</v>
       </c>
       <c r="B105" s="5"/>
@@ -3933,8 +3867,8 @@
       <c r="J105" s="8"/>
       <c r="K105" s="8"/>
     </row>
-    <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="5" t="n">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A106" s="5">
         <v>106</v>
       </c>
       <c r="B106" s="5"/>
@@ -3948,8 +3882,8 @@
       <c r="J106" s="8"/>
       <c r="K106" s="8"/>
     </row>
-    <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="5" t="n">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A107" s="5">
         <v>107</v>
       </c>
       <c r="B107" s="5"/>
@@ -3963,8 +3897,8 @@
       <c r="J107" s="8"/>
       <c r="K107" s="8"/>
     </row>
-    <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="5" t="n">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A108" s="5">
         <v>108</v>
       </c>
       <c r="B108" s="5"/>
@@ -3978,8 +3912,8 @@
       <c r="J108" s="8"/>
       <c r="K108" s="8"/>
     </row>
-    <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="5" t="n">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A109" s="5">
         <v>109</v>
       </c>
       <c r="B109" s="5"/>
@@ -3993,8 +3927,8 @@
       <c r="J109" s="8"/>
       <c r="K109" s="8"/>
     </row>
-    <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="5" t="n">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A110" s="5">
         <v>110</v>
       </c>
       <c r="B110" s="5"/>
@@ -4008,8 +3942,8 @@
       <c r="J110" s="8"/>
       <c r="K110" s="8"/>
     </row>
-    <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="5" t="n">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A111" s="5">
         <v>111</v>
       </c>
       <c r="B111" s="5"/>
@@ -4023,8 +3957,8 @@
       <c r="J111" s="8"/>
       <c r="K111" s="8"/>
     </row>
-    <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="5" t="n">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A112" s="5">
         <v>112</v>
       </c>
       <c r="B112" s="5"/>
@@ -4038,8 +3972,8 @@
       <c r="J112" s="8"/>
       <c r="K112" s="8"/>
     </row>
-    <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="5" t="n">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A113" s="5">
         <v>113</v>
       </c>
       <c r="B113" s="5"/>
@@ -4053,8 +3987,8 @@
       <c r="J113" s="8"/>
       <c r="K113" s="8"/>
     </row>
-    <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="5" t="n">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A114" s="5">
         <v>114</v>
       </c>
       <c r="B114" s="5"/>
@@ -4068,8 +4002,8 @@
       <c r="J114" s="8"/>
       <c r="K114" s="8"/>
     </row>
-    <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="5" t="n">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A115" s="5">
         <v>115</v>
       </c>
       <c r="B115" s="5"/>
@@ -4083,8 +4017,8 @@
       <c r="J115" s="8"/>
       <c r="K115" s="8"/>
     </row>
-    <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="5" t="n">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A116" s="5">
         <v>116</v>
       </c>
       <c r="B116" s="5"/>
@@ -4098,8 +4032,8 @@
       <c r="J116" s="8"/>
       <c r="K116" s="8"/>
     </row>
-    <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="5" t="n">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A117" s="5">
         <v>117</v>
       </c>
       <c r="B117" s="5"/>
@@ -4113,8 +4047,8 @@
       <c r="J117" s="8"/>
       <c r="K117" s="8"/>
     </row>
-    <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="5" t="n">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A118" s="5">
         <v>118</v>
       </c>
       <c r="B118" s="5"/>
@@ -4128,8 +4062,8 @@
       <c r="J118" s="8"/>
       <c r="K118" s="8"/>
     </row>
-    <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="5" t="n">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A119" s="5">
         <v>119</v>
       </c>
       <c r="B119" s="5"/>
@@ -4143,8 +4077,8 @@
       <c r="J119" s="8"/>
       <c r="K119" s="8"/>
     </row>
-    <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="5" t="n">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A120" s="5">
         <v>120</v>
       </c>
       <c r="B120" s="5"/>
@@ -4158,8 +4092,8 @@
       <c r="J120" s="8"/>
       <c r="K120" s="8"/>
     </row>
-    <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="5" t="n">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A121" s="5">
         <v>121</v>
       </c>
       <c r="B121" s="5"/>
@@ -4173,8 +4107,8 @@
       <c r="J121" s="8"/>
       <c r="K121" s="8"/>
     </row>
-    <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="5" t="n">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A122" s="5">
         <v>122</v>
       </c>
       <c r="B122" s="5"/>
@@ -4188,8 +4122,8 @@
       <c r="J122" s="8"/>
       <c r="K122" s="8"/>
     </row>
-    <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="5" t="n">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A123" s="5">
         <v>123</v>
       </c>
       <c r="B123" s="5"/>
@@ -4203,8 +4137,8 @@
       <c r="J123" s="8"/>
       <c r="K123" s="8"/>
     </row>
-    <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="5" t="n">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A124" s="5">
         <v>124</v>
       </c>
       <c r="B124" s="5"/>
@@ -4218,8 +4152,8 @@
       <c r="J124" s="8"/>
       <c r="K124" s="8"/>
     </row>
-    <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="5" t="n">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A125" s="5">
         <v>125</v>
       </c>
       <c r="B125" s="5"/>
@@ -4233,8 +4167,8 @@
       <c r="J125" s="8"/>
       <c r="K125" s="8"/>
     </row>
-    <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="5" t="n">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A126" s="5">
         <v>126</v>
       </c>
       <c r="B126" s="5"/>
@@ -4248,8 +4182,8 @@
       <c r="J126" s="8"/>
       <c r="K126" s="8"/>
     </row>
-    <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="5" t="n">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A127" s="5">
         <v>127</v>
       </c>
       <c r="B127" s="5"/>
@@ -4263,8 +4197,8 @@
       <c r="J127" s="8"/>
       <c r="K127" s="8"/>
     </row>
-    <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="5" t="n">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A128" s="5">
         <v>128</v>
       </c>
       <c r="B128" s="5"/>
@@ -4278,8 +4212,8 @@
       <c r="J128" s="8"/>
       <c r="K128" s="8"/>
     </row>
-    <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="5" t="n">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A129" s="5">
         <v>129</v>
       </c>
       <c r="B129" s="5"/>
@@ -4293,8 +4227,8 @@
       <c r="J129" s="8"/>
       <c r="K129" s="8"/>
     </row>
-    <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="5" t="n">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A130" s="5">
         <v>130</v>
       </c>
       <c r="B130" s="5"/>
@@ -4308,8 +4242,8 @@
       <c r="J130" s="8"/>
       <c r="K130" s="8"/>
     </row>
-    <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="5" t="n">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A131" s="5">
         <v>131</v>
       </c>
       <c r="B131" s="5"/>
@@ -4323,8 +4257,8 @@
       <c r="J131" s="8"/>
       <c r="K131" s="8"/>
     </row>
-    <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="5" t="n">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A132" s="5">
         <v>132</v>
       </c>
       <c r="B132" s="5"/>
@@ -4338,8 +4272,8 @@
       <c r="J132" s="8"/>
       <c r="K132" s="8"/>
     </row>
-    <row r="133" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="5" t="n">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A133" s="5">
         <v>133</v>
       </c>
       <c r="B133" s="5"/>
@@ -4353,8 +4287,8 @@
       <c r="J133" s="8"/>
       <c r="K133" s="8"/>
     </row>
-    <row r="134" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="5" t="n">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A134" s="5">
         <v>134</v>
       </c>
       <c r="B134" s="5"/>
@@ -4368,8 +4302,8 @@
       <c r="J134" s="8"/>
       <c r="K134" s="8"/>
     </row>
-    <row r="135" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="5" t="n">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A135" s="5">
         <v>135</v>
       </c>
       <c r="B135" s="5"/>
@@ -4383,8 +4317,8 @@
       <c r="J135" s="8"/>
       <c r="K135" s="8"/>
     </row>
-    <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="5" t="n">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A136" s="5">
         <v>136</v>
       </c>
       <c r="B136" s="5"/>
@@ -4398,8 +4332,8 @@
       <c r="J136" s="8"/>
       <c r="K136" s="8"/>
     </row>
-    <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="5" t="n">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A137" s="5">
         <v>137</v>
       </c>
       <c r="B137" s="5"/>
@@ -4413,8 +4347,8 @@
       <c r="J137" s="8"/>
       <c r="K137" s="8"/>
     </row>
-    <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="5" t="n">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A138" s="5">
         <v>138</v>
       </c>
       <c r="B138" s="5"/>
@@ -4428,8 +4362,8 @@
       <c r="J138" s="8"/>
       <c r="K138" s="8"/>
     </row>
-    <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="5" t="n">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A139" s="5">
         <v>139</v>
       </c>
       <c r="B139" s="5"/>
@@ -4443,8 +4377,8 @@
       <c r="J139" s="8"/>
       <c r="K139" s="8"/>
     </row>
-    <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="5" t="n">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A140" s="5">
         <v>140</v>
       </c>
       <c r="B140" s="5"/>
@@ -4458,8 +4392,8 @@
       <c r="J140" s="8"/>
       <c r="K140" s="8"/>
     </row>
-    <row r="141" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="5" t="n">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A141" s="5">
         <v>141</v>
       </c>
       <c r="B141" s="5"/>
@@ -4473,8 +4407,8 @@
       <c r="J141" s="8"/>
       <c r="K141" s="8"/>
     </row>
-    <row r="142" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="5" t="n">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A142" s="5">
         <v>142</v>
       </c>
       <c r="B142" s="5"/>
@@ -4488,8 +4422,8 @@
       <c r="J142" s="8"/>
       <c r="K142" s="8"/>
     </row>
-    <row r="143" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="5" t="n">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A143" s="5">
         <v>143</v>
       </c>
       <c r="B143" s="5"/>
@@ -4503,8 +4437,8 @@
       <c r="J143" s="8"/>
       <c r="K143" s="8"/>
     </row>
-    <row r="144" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="5" t="n">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A144" s="5">
         <v>144</v>
       </c>
       <c r="B144" s="5"/>
@@ -4518,8 +4452,8 @@
       <c r="J144" s="8"/>
       <c r="K144" s="8"/>
     </row>
-    <row r="145" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="5" t="n">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A145" s="5">
         <v>145</v>
       </c>
       <c r="B145" s="5"/>
@@ -4533,8 +4467,8 @@
       <c r="J145" s="8"/>
       <c r="K145" s="8"/>
     </row>
-    <row r="146" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="5" t="n">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A146" s="5">
         <v>146</v>
       </c>
       <c r="B146" s="5"/>
@@ -4548,8 +4482,8 @@
       <c r="J146" s="8"/>
       <c r="K146" s="8"/>
     </row>
-    <row r="147" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="5" t="n">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A147" s="5">
         <v>147</v>
       </c>
       <c r="B147" s="5"/>
@@ -4563,8 +4497,8 @@
       <c r="J147" s="8"/>
       <c r="K147" s="8"/>
     </row>
-    <row r="148" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="5" t="n">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A148" s="5">
         <v>148</v>
       </c>
       <c r="B148" s="5"/>
@@ -4578,8 +4512,8 @@
       <c r="J148" s="8"/>
       <c r="K148" s="8"/>
     </row>
-    <row r="149" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="5" t="n">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A149" s="5">
         <v>149</v>
       </c>
       <c r="B149" s="5"/>
@@ -4593,8 +4527,8 @@
       <c r="J149" s="8"/>
       <c r="K149" s="8"/>
     </row>
-    <row r="150" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="5" t="n">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A150" s="5">
         <v>150</v>
       </c>
       <c r="B150" s="5"/>
@@ -4608,8 +4542,8 @@
       <c r="J150" s="8"/>
       <c r="K150" s="8"/>
     </row>
-    <row r="151" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="5" t="n">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A151" s="5">
         <v>151</v>
       </c>
       <c r="B151" s="5"/>
@@ -4623,8 +4557,8 @@
       <c r="J151" s="8"/>
       <c r="K151" s="8"/>
     </row>
-    <row r="152" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="5" t="n">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A152" s="5">
         <v>152</v>
       </c>
       <c r="B152" s="5"/>
@@ -4638,8 +4572,8 @@
       <c r="J152" s="8"/>
       <c r="K152" s="8"/>
     </row>
-    <row r="153" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="5" t="n">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A153" s="5">
         <v>153</v>
       </c>
       <c r="B153" s="5"/>
@@ -4653,8 +4587,8 @@
       <c r="J153" s="8"/>
       <c r="K153" s="8"/>
     </row>
-    <row r="154" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="5" t="n">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A154" s="5">
         <v>154</v>
       </c>
       <c r="B154" s="5"/>
@@ -4668,8 +4602,8 @@
       <c r="J154" s="8"/>
       <c r="K154" s="8"/>
     </row>
-    <row r="155" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="5" t="n">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A155" s="5">
         <v>155</v>
       </c>
       <c r="B155" s="5"/>
@@ -4683,8 +4617,8 @@
       <c r="J155" s="8"/>
       <c r="K155" s="8"/>
     </row>
-    <row r="156" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="5" t="n">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A156" s="5">
         <v>156</v>
       </c>
       <c r="B156" s="5"/>
@@ -4698,8 +4632,8 @@
       <c r="J156" s="8"/>
       <c r="K156" s="8"/>
     </row>
-    <row r="157" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="5" t="n">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A157" s="5">
         <v>157</v>
       </c>
       <c r="B157" s="5"/>
@@ -4713,8 +4647,8 @@
       <c r="J157" s="8"/>
       <c r="K157" s="8"/>
     </row>
-    <row r="158" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="5" t="n">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A158" s="5">
         <v>158</v>
       </c>
       <c r="B158" s="5"/>
@@ -4728,8 +4662,8 @@
       <c r="J158" s="8"/>
       <c r="K158" s="8"/>
     </row>
-    <row r="159" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="5" t="n">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A159" s="5">
         <v>159</v>
       </c>
       <c r="B159" s="5"/>
@@ -4743,8 +4677,8 @@
       <c r="J159" s="8"/>
       <c r="K159" s="8"/>
     </row>
-    <row r="160" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="5" t="n">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A160" s="5">
         <v>160</v>
       </c>
       <c r="B160" s="5"/>
@@ -4758,8 +4692,8 @@
       <c r="J160" s="8"/>
       <c r="K160" s="8"/>
     </row>
-    <row r="161" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="5" t="n">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A161" s="5">
         <v>161</v>
       </c>
       <c r="B161" s="5"/>
@@ -4773,8 +4707,8 @@
       <c r="J161" s="8"/>
       <c r="K161" s="8"/>
     </row>
-    <row r="162" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="5" t="n">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A162" s="5">
         <v>162</v>
       </c>
       <c r="B162" s="5"/>
@@ -4788,8 +4722,8 @@
       <c r="J162" s="8"/>
       <c r="K162" s="8"/>
     </row>
-    <row r="163" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="5" t="n">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A163" s="5">
         <v>163</v>
       </c>
       <c r="B163" s="5"/>
@@ -4803,8 +4737,8 @@
       <c r="J163" s="8"/>
       <c r="K163" s="8"/>
     </row>
-    <row r="164" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A164" s="5" t="n">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A164" s="5">
         <v>164</v>
       </c>
       <c r="B164" s="5"/>
@@ -4818,8 +4752,8 @@
       <c r="J164" s="8"/>
       <c r="K164" s="8"/>
     </row>
-    <row r="165" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="5" t="n">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A165" s="5">
         <v>165</v>
       </c>
       <c r="B165" s="5"/>
@@ -4833,8 +4767,8 @@
       <c r="J165" s="8"/>
       <c r="K165" s="8"/>
     </row>
-    <row r="166" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A166" s="5" t="n">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A166" s="5">
         <v>166</v>
       </c>
       <c r="B166" s="5"/>
@@ -4848,8 +4782,8 @@
       <c r="J166" s="8"/>
       <c r="K166" s="8"/>
     </row>
-    <row r="167" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="5" t="n">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A167" s="5">
         <v>167</v>
       </c>
       <c r="B167" s="5"/>
@@ -4863,8 +4797,8 @@
       <c r="J167" s="8"/>
       <c r="K167" s="8"/>
     </row>
-    <row r="168" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A168" s="5" t="n">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A168" s="5">
         <v>168</v>
       </c>
       <c r="B168" s="5"/>
@@ -4878,8 +4812,8 @@
       <c r="J168" s="8"/>
       <c r="K168" s="8"/>
     </row>
-    <row r="169" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A169" s="5" t="n">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A169" s="5">
         <v>169</v>
       </c>
       <c r="B169" s="5"/>
@@ -4893,8 +4827,8 @@
       <c r="J169" s="8"/>
       <c r="K169" s="8"/>
     </row>
-    <row r="170" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A170" s="5" t="n">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A170" s="5">
         <v>170</v>
       </c>
       <c r="B170" s="5"/>
@@ -4908,8 +4842,8 @@
       <c r="J170" s="8"/>
       <c r="K170" s="8"/>
     </row>
-    <row r="171" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="5" t="n">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A171" s="5">
         <v>171</v>
       </c>
       <c r="B171" s="5"/>
@@ -4923,8 +4857,8 @@
       <c r="J171" s="8"/>
       <c r="K171" s="8"/>
     </row>
-    <row r="172" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="5" t="n">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A172" s="5">
         <v>172</v>
       </c>
       <c r="B172" s="5"/>
@@ -4938,8 +4872,8 @@
       <c r="J172" s="8"/>
       <c r="K172" s="8"/>
     </row>
-    <row r="173" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A173" s="5" t="n">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A173" s="5">
         <v>173</v>
       </c>
       <c r="B173" s="5"/>
@@ -4953,8 +4887,8 @@
       <c r="J173" s="8"/>
       <c r="K173" s="8"/>
     </row>
-    <row r="174" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="5" t="n">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A174" s="5">
         <v>174</v>
       </c>
       <c r="B174" s="5"/>
@@ -4968,8 +4902,8 @@
       <c r="J174" s="8"/>
       <c r="K174" s="8"/>
     </row>
-    <row r="175" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A175" s="5" t="n">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A175" s="5">
         <v>175</v>
       </c>
       <c r="B175" s="5"/>
@@ -4983,8 +4917,8 @@
       <c r="J175" s="8"/>
       <c r="K175" s="8"/>
     </row>
-    <row r="176" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="5" t="n">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A176" s="5">
         <v>176</v>
       </c>
       <c r="B176" s="5"/>
@@ -4998,8 +4932,8 @@
       <c r="J176" s="8"/>
       <c r="K176" s="8"/>
     </row>
-    <row r="177" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A177" s="5" t="n">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A177" s="5">
         <v>177</v>
       </c>
       <c r="B177" s="5"/>
@@ -5013,8 +4947,8 @@
       <c r="J177" s="8"/>
       <c r="K177" s="8"/>
     </row>
-    <row r="178" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="5" t="n">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A178" s="5">
         <v>178</v>
       </c>
       <c r="B178" s="5"/>
@@ -5028,8 +4962,8 @@
       <c r="J178" s="8"/>
       <c r="K178" s="8"/>
     </row>
-    <row r="179" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A179" s="5" t="n">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A179" s="5">
         <v>179</v>
       </c>
       <c r="B179" s="5"/>
@@ -5043,8 +4977,8 @@
       <c r="J179" s="8"/>
       <c r="K179" s="8"/>
     </row>
-    <row r="180" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="5" t="n">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A180" s="5">
         <v>180</v>
       </c>
       <c r="B180" s="5"/>
@@ -5058,8 +4992,8 @@
       <c r="J180" s="8"/>
       <c r="K180" s="8"/>
     </row>
-    <row r="181" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="5" t="n">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A181" s="5">
         <v>181</v>
       </c>
       <c r="B181" s="5"/>
@@ -5073,8 +5007,8 @@
       <c r="J181" s="8"/>
       <c r="K181" s="8"/>
     </row>
-    <row r="182" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A182" s="5" t="n">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A182" s="5">
         <v>182</v>
       </c>
       <c r="B182" s="5"/>
@@ -5088,8 +5022,8 @@
       <c r="J182" s="8"/>
       <c r="K182" s="8"/>
     </row>
-    <row r="183" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A183" s="5" t="n">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A183" s="5">
         <v>183</v>
       </c>
       <c r="B183" s="5"/>
@@ -5103,8 +5037,8 @@
       <c r="J183" s="8"/>
       <c r="K183" s="8"/>
     </row>
-    <row r="184" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="5" t="n">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A184" s="5">
         <v>184</v>
       </c>
       <c r="B184" s="5"/>
@@ -5118,8 +5052,8 @@
       <c r="J184" s="8"/>
       <c r="K184" s="8"/>
     </row>
-    <row r="185" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A185" s="5" t="n">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A185" s="5">
         <v>185</v>
       </c>
       <c r="B185" s="5"/>
@@ -5133,8 +5067,8 @@
       <c r="J185" s="8"/>
       <c r="K185" s="8"/>
     </row>
-    <row r="186" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="5" t="n">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A186" s="5">
         <v>186</v>
       </c>
       <c r="B186" s="5"/>
@@ -5148,8 +5082,8 @@
       <c r="J186" s="8"/>
       <c r="K186" s="8"/>
     </row>
-    <row r="187" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="5" t="n">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A187" s="5">
         <v>187</v>
       </c>
       <c r="B187" s="5"/>
@@ -5163,8 +5097,8 @@
       <c r="J187" s="8"/>
       <c r="K187" s="8"/>
     </row>
-    <row r="188" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="5" t="n">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A188" s="5">
         <v>188</v>
       </c>
       <c r="B188" s="5"/>
@@ -5179,14 +5113,8 @@
       <c r="K188" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K188"/>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <autoFilter ref="A1:K188" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>